--- a/Pelis.xlsx
+++ b/Pelis.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="1826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
   <si>
     <t>Numero</t>
   </si>
@@ -5506,6 +5506,906 @@
   </si>
   <si>
     <t>Keenen Ivory Wayans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bring Her Back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danny Philippou, Michael Philippou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find Me Guilty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cabin in the Woods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canadá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Life of Chuck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clown in a Cornfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anand Tucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Irlanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ladykillers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Coen, Ethan Coen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballerina (From the World of John Wick)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sisu: Road to Revenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finlandia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft &amp; Quiet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth de Araújo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El secreto de Marrowbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrzej Żuławski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francia / Alemania Occidental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bugonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Reino Unido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El coso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Wong Foo, Thanks for Everything! Julie Newmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beeban Kidron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdimar Jóhannsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Islandia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo de pagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felipe Wein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crimewave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Sheep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Me, Myself &amp; Irene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobby Farrelly, Peter Farrelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming Led Zeppelin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernard MacMahon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reino Unido / USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raising Arizona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Amateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boys Don't Cry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimberly Peirce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un peso, un dólar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Condron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pieces (Mil gritos tiene la noche)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Piquer Simón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evil Dead II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford v Ferrari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Agente Secreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vida útil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico Veiroj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Smashing Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benny Safdie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo el año es Navidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gattaca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Niccol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nighthawks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruce Malmuth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sex Tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kill Bill: The Whole Bloody Affair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The NeverEnding Story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alemania Occidental / USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicos ricos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariano Galperín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Fortune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aziz Ansari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle of the Sexes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Dayton, Valerie Faris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghostbusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redux Redux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin McManus, Matthew McManus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marty Supreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Safdie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El extraño viaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Fernán Gómez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Showman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El tema del verano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo Stoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruguay / Argentina / Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacurau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kleber Mendonça Filho, Juliano Dornelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talk to Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late Night with the Devil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Cairnes, Colin Cairnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't Die: The Man Who Wants to Live Forever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryce Dallas Howard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuestra tierra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Vanishing (Spoorloos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Sluizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Países Bajos / Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Running Man</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the President's Men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alan J. Pakula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Secret!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jim Abrahams, David Zucker, Jerry Zucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scream 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Williamson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Michael Glaser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Boondock Saints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troy Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn After Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send Help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Amazing Transplant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doris Wishman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promising Young Woman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of War</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ciénaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El otro hermano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel Adrián Caetano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Real Pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Eisenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Polonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rough Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucia Aniello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En retirada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Carlos Desanzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready or Not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Bettinelli-Olpin, Tyler Gillett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Canadá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank You for Smoking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yiya Murano: muerte a la hora del té</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medianeras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustavo Taretto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenacious D in The Pick of Destiny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Últimos días de la víctima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La parte del león</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Den of Thieves 2: Pantera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Gudegast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traslados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolás Gil Lavedra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Taking of Pelham One Two Three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tin Soldier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Furman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death Becomes Her</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Curious Case of Benjamin Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Star Chamber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Hyams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Taking of Pelham 123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hannibal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Lapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradley King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un lugar en el mundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina / Uruguay / España</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desearás al hombre de tu hermana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Way Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roger Donaldson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Bride!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maggie Gyllenhaal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Quién puede matar a un niño?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narciso Ibáñez Serrador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DodgeBall: A True Underdog Story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rawson Marshall Thurber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Man</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladies First</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thea Sharrock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Royal Tenenbaums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wes Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Simple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El vampiro negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Román Viñoly Barreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Wick: Chapter 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It Follows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrebato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iván Zulueta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Wick: Chapter 3 – Parabellum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They Will Kill You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirill Sokolov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortal Kombat II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Wick: Chapter 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 40-Year-Old Virgin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vampire humaniste cherche suicidaire consentant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ariane Louis-Seize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghost World</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Zwigoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Reino Unido / Alemania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foul Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colin Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul W. S. Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undercover Brother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soñar, soñar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Favio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekend at Bernie's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortal Kombat: Annihilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equilibrium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Wimmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shampoo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hal Ashby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikey and Nicky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elaine May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunny Lake Is Missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otto Preminger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready or Not 2: Here I Come</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backrooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kane Parsons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antiviral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Cronenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El partido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Cabral, Santiago Franco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let the Corpses Tan (Laissez bronzer les cadavres)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hélène Cattet, Bruno Forzani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bélgica / Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Alemania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Nightmare on Elm Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But I'm a Cheerleader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Babbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleepers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal Affairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Figgis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razorback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russell Mulcahy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurovision Song Contest: The Story of Fire Saga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Dobkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nineteen Eighty-Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Radford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sheep Detectives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Balda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scary Movie 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Tiddes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los jóvenes viejos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodolfo Kuhn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Nightmare on Elm Street 2: Freddy's Revenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Sholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electra Glide in Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James William Guercio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Nightmare on Elm Street 3: Dream Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chuck Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stuart Gordon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deuce Bigalow: European Gigolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Bigelow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Países Bajos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dicha en movimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxi Gutiérrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Nightmare on Elm Street 4: The Dream Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renny Harlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Nightmare on Elm Street 5: The Dream Child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal Attraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Another Teen Movie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Gallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy's Dead: The Final Nightmare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachel Talalay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walter Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wes Craven's New Nightmare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hot Chick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Brady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling Thunder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Flynn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo de valientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damián Szifrón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy vs. Jason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronny Yu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Canadá / Italia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boogie Nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Bayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dawn of the Dead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA / Canadá / Japón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would You Rather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Guy Levy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experiment in Terror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fritz the Cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ralph Bakshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyes Without a Face (Les yeux sans visage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georges Franju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francia / Italia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perdita Durango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">España / México / USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barreda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniela Goggi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vampyros Lesbos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesús Franco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alemania Occidental / España</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaXXXine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super Troopers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jay Chandrasekhar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Rocky Horror Picture Show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A History of Violence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Attenborough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hausu (House)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobuhiko Ôbayashi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japón</t>
   </si>
 </sst>
 </file>
@@ -30366,7 +31266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="15.0" customHeight="1">
+    <row r="2">
       <c r="A2" s="2">
         <v>1.0</v>
       </c>
@@ -30374,16 +31274,16 @@
         <v>46026.0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1713</v>
+        <v>1826</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1716</v>
+        <v>1827</v>
       </c>
       <c r="E2" s="4">
         <v>2025.0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -30394,7 +31294,7 @@
         <v>46027.0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1719</v>
+        <v>1828</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>203</v>
@@ -30414,7 +31314,7 @@
         <v>46028.0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>932</v>
+        <v>1829</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>933</v>
@@ -30443,7 +31343,7 @@
         <v>2010.0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1724</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="6">
@@ -30454,7 +31354,7 @@
         <v>46030.0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1726</v>
+        <v>1831</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>1727</v>
@@ -30474,7 +31374,7 @@
         <v>46032.0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1730</v>
+        <v>1832</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>1732</v>
@@ -30497,13 +31397,13 @@
         <v>1733</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1734</v>
+        <v>1833</v>
       </c>
       <c r="E8" s="4">
-        <v>1921.0</v>
+        <v>2010.0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>11</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="9">
@@ -30514,10 +31414,10 @@
         <v>46040.0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1736</v>
+        <v>1835</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>156</v>
+        <v>1836</v>
       </c>
       <c r="E9" s="4">
         <v>2004.0</v>
@@ -30554,7 +31454,7 @@
         <v>46046.0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1742</v>
+        <v>1837</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>1743</v>
@@ -30594,7 +31494,7 @@
         <v>46047.0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1747</v>
+        <v>1838</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>1302</v>
@@ -30603,7 +31503,7 @@
         <v>2025.0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1750</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="14">
@@ -30614,10 +31514,10 @@
         <v>46047.0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1751</v>
+        <v>1840</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1171</v>
+        <v>1841</v>
       </c>
       <c r="E14" s="4">
         <v>2022.0</v>
@@ -30633,7 +31533,7 @@
       <c r="B15" s="3">
         <v>46048.0</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>1753</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -30673,8 +31573,8 @@
       <c r="B17" s="3">
         <v>46049.0</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>1760</v>
+      <c r="C17" s="4" t="s">
+        <v>1842</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>1762</v>
@@ -30697,1551 +31597,3734 @@
         <v>1763</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1765</v>
+        <v>1843</v>
       </c>
       <c r="E18" s="4">
         <v>1981.0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>76</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
         <v>18.0</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="B19" s="3">
+        <v>46051.0</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>1846</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
         <v>19.0</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="B20" s="3">
+        <v>46053.0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2014.0</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4">
         <v>20.0</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="B21" s="3">
+        <v>46055.0</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2022.0</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
         <v>21.0</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="B22" s="3">
+        <v>46056.0</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1995.0</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4">
         <v>22.0</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="B23" s="3">
+        <v>46057.0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E23" s="4">
+        <v>2021.0</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>1854</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
         <v>23.0</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="B24" s="3">
+        <v>46058.0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4">
         <v>24.0</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="B25" s="3">
+        <v>46059.0</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1985.0</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
         <v>25.0</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="B26" s="3">
+        <v>46060.0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2006.0</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4">
         <v>26.0</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="B27" s="3">
+        <v>46061.0</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
         <v>27.0</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="B28" s="3">
+        <v>46062.0</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>1864</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4">
         <v>28.0</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="B29" s="3">
+        <v>46063.0</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
         <v>29.0</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="B30" s="3">
+        <v>46065.0</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>1846</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4">
         <v>30.0</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" ht="17.25" customHeight="1">
+      <c r="B31" s="3">
+        <v>46070.0</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E31" s="4">
+        <v>1999.0</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="2">
         <v>31.0</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="B32" s="3">
+        <v>46071.0</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>1871</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2007.0</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4">
         <v>32.0</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="B33" s="3">
+        <v>46072.0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E33" s="4">
+        <v>1982.0</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
         <v>33.0</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+      <c r="B34" s="3">
+        <v>46074.0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4">
         <v>34.0</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="B35" s="3">
+        <v>46075.0</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E35" s="4">
+        <v>2019.0</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
         <v>35.0</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="B36" s="3">
+        <v>46076.0</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4">
         <v>36.0</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="B37" s="3">
+        <v>46077.0</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2010.0</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>809</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
         <v>37.0</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="B38" s="3">
+        <v>46078.0</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4">
         <v>38.0</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="B39" s="3">
+        <v>46079.0</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E39" s="4">
+        <v>2018.0</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
         <v>39.0</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="B40" s="3">
+        <v>46080.0</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1997.0</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4">
         <v>40.0</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="B41" s="3">
+        <v>46081.0</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1981.0</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
         <v>41.0</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="B42" s="3">
+        <v>46081.0</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1982.0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4">
         <v>42.0</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="B43" s="3">
+        <v>46082.0</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2014.0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
         <v>43.0</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="B44" s="3">
+        <v>46082.0</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1999.0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4">
         <v>44.0</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="B45" s="3">
+        <v>46084.0</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
         <v>45.0</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="B46" s="3">
+        <v>46086.0</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>1890</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4">
         <v>46.0</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="B47" s="3">
+        <v>46087.0</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E47" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
         <v>47.0</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+      <c r="B48" s="3">
+        <v>46088.0</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E48" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4">
         <v>48.0</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="B49" s="3">
+        <v>46088.0</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E49" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>1846</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
         <v>49.0</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="B50" s="3">
+        <v>46088.0</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4">
         <v>50.0</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="B51" s="3">
+        <v>46089.0</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E51" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
         <v>51.0</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="B52" s="3">
+        <v>46091.0</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E52" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4">
         <v>52.0</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="B53" s="3">
+        <v>46093.0</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E53" s="4">
+        <v>1964.0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
         <v>53.0</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+      <c r="B54" s="3">
+        <v>46094.0</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1996.0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4">
         <v>54.0</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="4"/>
+      <c r="B55" s="3">
+        <v>46095.0</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E55" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
         <v>55.0</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="16"/>
+      <c r="B56" s="3">
+        <v>46095.0</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E56" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>1908</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4">
         <v>56.0</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="4"/>
+      <c r="B57" s="3">
+        <v>46095.0</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E57" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
         <v>57.0</v>
       </c>
-      <c r="B58" s="3"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="B58" s="3">
+        <v>46096.0</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E58" s="4">
+        <v>2019.0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4">
         <v>58.0</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="B59" s="3">
+        <v>46096.0</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E59" s="4">
+        <v>2022.0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
         <v>59.0</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="B60" s="3">
+        <v>46097.0</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E60" s="4">
+        <v>2023.0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4">
         <v>60.0</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
+      <c r="B61" s="3">
+        <v>46100.0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E61" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
         <v>61.0</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
+      <c r="B62" s="3">
+        <v>46101.0</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E62" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4">
         <v>62.0</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+      <c r="B63" s="3">
+        <v>46102.0</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E63" s="4">
+        <v>1988.0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>1919</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2">
         <v>63.0</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+      <c r="B64" s="3">
+        <v>46102.0</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4">
         <v>64.0</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+      <c r="B65" s="3">
+        <v>46103.0</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E65" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
         <v>65.0</v>
       </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="B66" s="3">
+        <v>46103.0</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4">
         <v>66.0</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
+      <c r="B67" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E67" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
         <v>67.0</v>
       </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+      <c r="B68" s="3">
+        <v>46105.0</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E68" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4">
         <v>68.0</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="B69" s="3">
+        <v>46109.0</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E69" s="4">
+        <v>1999.0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
         <v>69.0</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="B70" s="3">
+        <v>46110.0</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E70" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4">
         <v>70.0</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="B71" s="3">
+        <v>46110.0</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E71" s="4">
+        <v>2008.0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2">
         <v>71.0</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
+      <c r="B72" s="3">
+        <v>46110.0</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E72" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4">
         <v>72.0</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="B73" s="3">
+        <v>46111.0</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1970.0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2">
         <v>73.0</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+      <c r="B74" s="3">
+        <v>46111.0</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="E74" s="4">
+        <v>2020.0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>1864</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4">
         <v>74.0</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-    </row>
-    <row r="76" ht="15.0" customHeight="1">
+      <c r="B75" s="3">
+        <v>46114.0</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E75" s="4">
+        <v>1982.0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="2">
         <v>75.0</v>
       </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+      <c r="B76" s="3">
+        <v>46121.0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E76" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4">
         <v>76.0</v>
       </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
+      <c r="B77" s="3">
+        <v>46122.0</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E77" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" s="2">
         <v>77.0</v>
       </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="B78" s="3">
+        <v>46123.0</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E78" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4">
         <v>78.0</v>
       </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="B79" s="3">
+        <v>46128.0</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E79" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
         <v>79.0</v>
       </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
+      <c r="B80" s="3">
+        <v>46129.0</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="E80" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4">
         <v>80.0</v>
       </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+      <c r="B81" s="3">
+        <v>46130.0</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E81" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>1943</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2">
         <v>81.0</v>
       </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
+      <c r="B82" s="3">
+        <v>46131.0</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E82" s="4">
+        <v>2016.0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4">
         <v>82.0</v>
       </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
+      <c r="B83" s="3">
+        <v>46131.0</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E83" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
         <v>83.0</v>
       </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
+      <c r="B84" s="3">
+        <v>46135.0</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E84" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4">
         <v>84.0</v>
       </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
+      <c r="B85" s="3">
+        <v>46137.0</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E85" s="4">
+        <v>2019.0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1951</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2">
         <v>85.0</v>
       </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
+      <c r="B86" s="3">
+        <v>46138.0</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E86" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4">
         <v>86.0</v>
       </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
+      <c r="B87" s="3">
+        <v>46138.0</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
         <v>87.0</v>
       </c>
-      <c r="B88" s="3"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
+      <c r="B88" s="3">
+        <v>46142.0</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E88" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4">
         <v>88.0</v>
       </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="B89" s="3">
+        <v>46143.0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E89" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2">
         <v>89.0</v>
       </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
+      <c r="B90" s="3">
+        <v>46144.0</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E90" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>1864</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4">
         <v>90.0</v>
       </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
+      <c r="B91" s="3">
+        <v>46144.0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E91" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2">
         <v>91.0</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
+      <c r="B92" s="3">
+        <v>46145.0</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E92" s="4">
+        <v>2006.0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4">
         <v>92.0</v>
       </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
+      <c r="B93" s="3">
+        <v>46146.0</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93" s="4">
+        <v>1982.0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2">
         <v>93.0</v>
       </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
+      <c r="B94" s="3">
+        <v>46148.0</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94" s="4">
+        <v>1978.0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4">
         <v>94.0</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="B95" s="3">
+        <v>46151.0</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E95" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2">
         <v>95.0</v>
       </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
+      <c r="B96" s="3">
+        <v>46151.0</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E96" s="4">
+        <v>2013.0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4">
         <v>96.0</v>
       </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="B97" s="3">
+        <v>46152.0</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="E97" s="4">
+        <v>1974.0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2">
         <v>97.0</v>
       </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
+      <c r="B98" s="3">
+        <v>46155.0</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E98" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4">
         <v>98.0</v>
       </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="B99" s="3">
+        <v>46157.0</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E99" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2">
         <v>99.0</v>
       </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
+      <c r="B100" s="3">
+        <v>46158.0</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="E100" s="4">
+        <v>1974.0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4">
         <v>100.0</v>
       </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="B101" s="3">
+        <v>46158.0</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E101" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2">
         <v>101.0</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
+      <c r="B102" s="3">
+        <v>46158.0</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E102" s="4">
+        <v>1999.0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4">
         <v>102.0</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
+      <c r="B103" s="3">
+        <v>46159.0</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="E103" s="4">
+        <v>1992.0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2">
         <v>103.0</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="B104" s="3">
+        <v>46159.0</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E104" s="4">
+        <v>2008.0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4">
         <v>104.0</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
+      <c r="B105" s="3">
+        <v>46162.0</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E105" s="4">
+        <v>1996.0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2">
         <v>105.0</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
+      <c r="B106" s="3">
+        <v>46164.0</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1983.0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4">
         <v>106.0</v>
       </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="B107" s="3">
+        <v>46165.0</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1990.0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2">
         <v>107.0</v>
       </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
+      <c r="B108" s="3">
+        <v>46166.0</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="4">
+        <v>1983.0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4">
         <v>108.0</v>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
+      <c r="B109" s="3">
+        <v>46167.0</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="E109" s="4">
+        <v>2009.0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2">
         <v>109.0</v>
       </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="B110" s="3">
+        <v>46167.0</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4">
         <v>110.0</v>
       </c>
-      <c r="B111" s="3"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="B111" s="3">
+        <v>46170.0</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>1976</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E111" s="4">
+        <v>2014.0</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2">
         <v>111.0</v>
       </c>
-      <c r="B112" s="3"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
+      <c r="B112" s="3">
+        <v>46171.0</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E112" s="4">
+        <v>1992.0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>1979</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4">
         <v>112.0</v>
       </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
+      <c r="B113" s="3">
+        <v>46172.0</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E113" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2">
         <v>113.0</v>
       </c>
-      <c r="B114" s="3"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="B114" s="3">
+        <v>46173.0</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E114" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4">
         <v>114.0</v>
       </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
+      <c r="B115" s="3">
+        <v>46173.0</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E115" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2">
         <v>115.0</v>
       </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
+      <c r="B116" s="3">
+        <v>46174.0</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E116" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4">
         <v>116.0</v>
       </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
+      <c r="B117" s="3">
+        <v>46178.0</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="E117" s="4">
+        <v>1988.0</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2">
         <v>117.0</v>
       </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
+      <c r="B118" s="3">
+        <v>46179.0</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E118" s="4">
+        <v>2004.0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4">
         <v>118.0</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
+      <c r="B119" s="3">
+        <v>46179.0</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E119" s="4">
+        <v>2014.0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2">
         <v>119.0</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
+      <c r="B120" s="3">
+        <v>46180.0</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E120" s="4">
+        <v>2006.0</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4">
         <v>120.0</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
+      <c r="B121" s="3">
+        <v>46180.0</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E121" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2">
         <v>121.0</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
+      <c r="B122" s="3">
+        <v>46180.0</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E122" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4">
         <v>122.0</v>
       </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
+      <c r="B123" s="3">
+        <v>46183.0</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E123" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2">
         <v>123.0</v>
       </c>
-      <c r="B124" s="3"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
+      <c r="B124" s="3">
+        <v>46184.0</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E124" s="4">
+        <v>1953.0</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4">
         <v>124.0</v>
       </c>
-      <c r="B125" s="3"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
+      <c r="B125" s="3">
+        <v>46184.0</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E125" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2">
         <v>125.0</v>
       </c>
-      <c r="B126" s="3"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
+      <c r="B126" s="3">
+        <v>46185.0</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="E126" s="4">
+        <v>2021.0</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4">
         <v>126.0</v>
       </c>
-      <c r="B127" s="3"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
+      <c r="B127" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E127" s="4">
+        <v>2014.0</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2">
         <v>127.0</v>
       </c>
-      <c r="B128" s="3"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
+      <c r="B128" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E128" s="4">
+        <v>1979.0</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="2">
+      <c r="A129" s="4">
         <v>128.0</v>
       </c>
-      <c r="B129" s="3"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
+      <c r="B129" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E129" s="4">
+        <v>2019.0</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="4">
+      <c r="A130" s="2">
         <v>129.0</v>
       </c>
-      <c r="B130" s="3"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
+      <c r="B130" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E130" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4">
         <v>130.0</v>
       </c>
-      <c r="B131" s="3"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
+      <c r="B131" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="E131" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>2005</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2">
         <v>131.0</v>
       </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
+      <c r="B132" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E132" s="4">
+        <v>2023.0</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="2">
+      <c r="A133" s="4">
         <v>132.0</v>
       </c>
-      <c r="B133" s="3"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
+      <c r="B133" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E133" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2">
         <v>133.0</v>
       </c>
-      <c r="B134" s="3"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
+      <c r="B134" s="3">
+        <v>46188.0</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>2009</v>
+      </c>
+      <c r="E134" s="4">
+        <v>2023.0</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>1830</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4">
         <v>134.0</v>
       </c>
-      <c r="B135" s="3"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="B135" s="3">
+        <v>46191.0</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="E135" s="4">
+        <v>2011.0</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="4">
+      <c r="A136" s="2">
         <v>135.0</v>
       </c>
-      <c r="B136" s="3"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
+      <c r="B136" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E136" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>2013</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="2">
+      <c r="A137" s="4">
         <v>136.0</v>
       </c>
-      <c r="B137" s="3"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
+      <c r="B137" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E137" s="4">
+        <v>1978.0</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2">
         <v>137.0</v>
       </c>
-      <c r="B138" s="3"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
+      <c r="B138" s="3">
+        <v>46197.0</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="4">
+        <v>2020.0</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="2">
+      <c r="A139" s="4">
         <v>138.0</v>
       </c>
-      <c r="B139" s="3"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
+      <c r="B139" s="3">
+        <v>46200.0</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>2016</v>
+      </c>
+      <c r="E139" s="4">
+        <v>1995.0</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="4">
+      <c r="A140" s="2">
         <v>139.0</v>
       </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
+      <c r="B140" s="3">
+        <v>46200.0</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="E140" s="4">
+        <v>2002.0</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4">
         <v>140.0</v>
       </c>
-      <c r="B141" s="3"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
+      <c r="B141" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E141" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2">
         <v>141.0</v>
       </c>
-      <c r="B142" s="3"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
+      <c r="B142" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="E142" s="4">
+        <v>1989.0</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="2">
+      <c r="A143" s="4">
         <v>142.0</v>
       </c>
-      <c r="B143" s="3"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
+      <c r="B143" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="E143" s="4">
+        <v>1997.0</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2">
         <v>143.0</v>
       </c>
-      <c r="B144" s="3"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
+      <c r="B144" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>2023</v>
+      </c>
+      <c r="E144" s="4">
+        <v>2002.0</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4">
         <v>144.0</v>
       </c>
-      <c r="B145" s="3"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
+      <c r="B145" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E145" s="4">
+        <v>1975.0</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="4">
+      <c r="A146" s="2">
         <v>145.0</v>
       </c>
-      <c r="B146" s="3"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
+      <c r="B146" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E146" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="2">
+      <c r="A147" s="4">
         <v>146.0</v>
       </c>
-      <c r="B147" s="3"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
+      <c r="B147" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E147" s="4">
+        <v>1965.0</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2">
         <v>147.0</v>
       </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
+      <c r="B148" s="3">
+        <v>46212.0</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E148" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="2">
+      <c r="A149" s="4">
         <v>148.0</v>
       </c>
-      <c r="B149" s="3"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="8"/>
+      <c r="B149" s="3">
+        <v>46213.0</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E149" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="4">
+      <c r="A150" s="2">
         <v>149.0</v>
       </c>
-      <c r="B150" s="3"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="11"/>
-      <c r="F150" s="11"/>
+      <c r="B150" s="3">
+        <v>46214.0</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E150" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="2">
+      <c r="A151" s="4">
         <v>150.0</v>
       </c>
-      <c r="B151" s="3"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="11"/>
-      <c r="F151" s="11"/>
+      <c r="B151" s="3">
+        <v>46215.0</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E151" s="4">
+        <v>2012.0</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>1830</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="11">
+      <c r="A152" s="2">
         <v>151.0</v>
       </c>
-      <c r="B152" s="3"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
+      <c r="B152" s="3">
+        <v>46217.0</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E152" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="11">
+      <c r="A153" s="4">
         <v>152.0</v>
       </c>
-      <c r="B153" s="3"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
+      <c r="B153" s="3">
+        <v>46220.0</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E153" s="4">
+        <v>2017.0</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>2040</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="11">
+      <c r="A154" s="2">
         <v>153.0</v>
       </c>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
+      <c r="B154" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" s="4">
+        <v>2012.0</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="11">
+      <c r="A155" s="4">
         <v>154.0</v>
       </c>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
+      <c r="B155" s="3">
+        <v>46221.0</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="E155" s="4">
+        <v>2006.0</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>2041</v>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="11">
+      <c r="A156" s="2">
         <v>155.0</v>
       </c>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
+      <c r="B156" s="3">
+        <v>46222.0</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E156" s="4">
+        <v>2006.0</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="11">
+      <c r="A157" s="4">
         <v>156.0</v>
       </c>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="11"/>
+      <c r="B157" s="3">
+        <v>46224.0</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="11">
+      <c r="A158" s="2">
         <v>157.0</v>
       </c>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
-      <c r="F158" s="11"/>
+      <c r="B158" s="3">
+        <v>46225.0</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E158" s="4">
+        <v>1999.0</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="11">
+      <c r="A159" s="4">
         <v>158.0</v>
       </c>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11"/>
+      <c r="B159" s="3">
+        <v>46226.0</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E159" s="4">
+        <v>1996.0</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="11">
+      <c r="A160" s="2">
         <v>159.0</v>
       </c>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
+      <c r="B160" s="3">
+        <v>46226.0</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E160" s="4">
+        <v>1990.0</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="11">
+      <c r="A161" s="4">
         <v>160.0</v>
       </c>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
-      <c r="F161" s="11"/>
+      <c r="B161" s="3">
+        <v>46227.0</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E161" s="4">
+        <v>1990.0</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="11">
+      <c r="A162" s="2">
         <v>161.0</v>
       </c>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
-      <c r="F162" s="11"/>
+      <c r="B162" s="3">
+        <v>46228.0</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E162" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="11">
+      <c r="A163" s="4">
         <v>162.0</v>
       </c>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
-      <c r="E163" s="11"/>
-      <c r="F163" s="11"/>
+      <c r="B163" s="3">
+        <v>46228.0</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E163" s="4">
+        <v>2020.0</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="11">
+      <c r="A164" s="2">
         <v>163.0</v>
       </c>
-      <c r="B164" s="11"/>
-      <c r="C164" s="11"/>
-      <c r="D164" s="11"/>
-      <c r="E164" s="11"/>
-      <c r="F164" s="11"/>
+      <c r="B164" s="3">
+        <v>46229.0</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E164" s="4">
+        <v>1984.0</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="11">
+      <c r="A165" s="4">
         <v>164.0</v>
       </c>
-      <c r="B165" s="11"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="11"/>
-      <c r="E165" s="11"/>
-      <c r="F165" s="11"/>
+      <c r="B165" s="3">
+        <v>46229.0</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E165" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="11">
+      <c r="A166" s="2">
         <v>165.0</v>
       </c>
-      <c r="B166" s="11"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="11"/>
-      <c r="E166" s="11"/>
-      <c r="F166" s="11"/>
+      <c r="B166" s="3">
+        <v>46229.0</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E166" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="11">
+      <c r="A167" s="4">
         <v>166.0</v>
       </c>
-      <c r="B167" s="11"/>
-      <c r="C167" s="11"/>
-      <c r="D167" s="11"/>
-      <c r="E167" s="11"/>
-      <c r="F167" s="11"/>
+      <c r="B167" s="3">
+        <v>46231.0</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E167" s="4">
+        <v>1962.0</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="11">
+      <c r="A168" s="2">
         <v>167.0</v>
       </c>
-      <c r="B168" s="11"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="11"/>
-      <c r="E168" s="11"/>
-      <c r="F168" s="11"/>
+      <c r="B168" s="3">
+        <v>46231.0</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E168" s="4">
+        <v>1985.0</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="11">
+      <c r="A169" s="4">
         <v>168.0</v>
       </c>
-      <c r="B169" s="11"/>
-      <c r="C169" s="11"/>
-      <c r="D169" s="11"/>
-      <c r="E169" s="11"/>
-      <c r="F169" s="11"/>
+      <c r="B169" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E169" s="4">
+        <v>1976.0</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="11">
+      <c r="A170" s="2">
         <v>169.0</v>
       </c>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="11"/>
-      <c r="E170" s="11"/>
-      <c r="F170" s="11"/>
+      <c r="B170" s="3">
+        <v>46239.0</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E170" s="4">
+        <v>1973.0</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="11">
+      <c r="A171" s="4">
         <v>170.0</v>
       </c>
-      <c r="B171" s="11"/>
-      <c r="C171" s="11"/>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
-      <c r="F171" s="11"/>
+      <c r="B171" s="3">
+        <v>46240.0</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E171" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="11">
+      <c r="A172" s="2">
         <v>171.0</v>
       </c>
-      <c r="B172" s="11"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="11"/>
-      <c r="E172" s="11"/>
-      <c r="F172" s="11"/>
+      <c r="B172" s="3">
+        <v>46241.0</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E172" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4">
+        <v>172.0</v>
+      </c>
+      <c r="B173" s="3">
+        <v>46241.0</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E173" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2">
+        <v>173.0</v>
+      </c>
+      <c r="B174" s="3">
+        <v>46242.0</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E174" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4">
+        <v>174.0</v>
+      </c>
+      <c r="B175" s="3">
+        <v>46242.0</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E175" s="4">
+        <v>1988.0</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2">
+        <v>175.0</v>
+      </c>
+      <c r="B176" s="3">
+        <v>46243.0</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E176" s="4">
+        <v>1989.0</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4">
+        <v>176.0</v>
+      </c>
+      <c r="B177" s="3">
+        <v>46247.0</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="E177" s="4">
+        <v>1987.0</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2">
+        <v>177.0</v>
+      </c>
+      <c r="B178" s="3">
+        <v>46248.0</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E178" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4">
+        <v>178.0</v>
+      </c>
+      <c r="B179" s="3">
+        <v>46248.0</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E179" s="4">
+        <v>1991.0</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2">
+        <v>179.0</v>
+      </c>
+      <c r="B180" s="3">
+        <v>46248.0</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="E180" s="4">
+        <v>1981.0</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4">
+        <v>180.0</v>
+      </c>
+      <c r="B181" s="3">
+        <v>46249.0</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E181" s="4">
+        <v>1979.0</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2">
+        <v>181.0</v>
+      </c>
+      <c r="B182" s="3">
+        <v>46249.0</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="4">
+        <v>1994.0</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4">
+        <v>182.0</v>
+      </c>
+      <c r="B183" s="3">
+        <v>46249.0</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E183" s="4">
+        <v>2002.0</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2">
+        <v>183.0</v>
+      </c>
+      <c r="B184" s="3">
+        <v>46250.0</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E184" s="4">
+        <v>1977.0</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4">
+        <v>184.0</v>
+      </c>
+      <c r="B185" s="3">
+        <v>46250.0</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E185" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2">
+        <v>185.0</v>
+      </c>
+      <c r="B186" s="3">
+        <v>46251.0</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E186" s="4">
+        <v>2003.0</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4">
+        <v>186.0</v>
+      </c>
+      <c r="B187" s="3">
+        <v>46251.0</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E187" s="4">
+        <v>1997.0</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2">
+        <v>187.0</v>
+      </c>
+      <c r="B188" s="3">
+        <v>46251.0</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E188" s="4">
+        <v>2022.0</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4">
+        <v>188.0</v>
+      </c>
+      <c r="B189" s="3">
+        <v>46253.0</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E189" s="4">
+        <v>2010.0</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2">
+        <v>189.0</v>
+      </c>
+      <c r="B190" s="3">
+        <v>46254.0</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="E190" s="4">
+        <v>2004.0</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4">
+        <v>190.0</v>
+      </c>
+      <c r="B191" s="3">
+        <v>46255.0</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E191" s="4">
+        <v>2012.0</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2">
+        <v>191.0</v>
+      </c>
+      <c r="B192" s="3">
+        <v>46255.0</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E192" s="4">
+        <v>2022.0</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4">
+        <v>192.0</v>
+      </c>
+      <c r="B193" s="3">
+        <v>46256.0</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E193" s="4">
+        <v>1962.0</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2">
+        <v>193.0</v>
+      </c>
+      <c r="B194" s="3">
+        <v>46256.0</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E194" s="4">
+        <v>1972.0</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4">
+        <v>194.0</v>
+      </c>
+      <c r="B195" s="3">
+        <v>46261.0</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E195" s="4">
+        <v>1960.0</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2">
+        <v>195.0</v>
+      </c>
+      <c r="B196" s="3">
+        <v>46262.0</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E196" s="4">
+        <v>1997.0</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4">
+        <v>196.0</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46264.0</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E197" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2">
+        <v>197.0</v>
+      </c>
+      <c r="B198" s="3">
+        <v>46265.0</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E198" s="4">
+        <v>1971.0</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4">
+        <v>198.0</v>
+      </c>
+      <c r="B199" s="3">
+        <v>46266.0</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E199" s="4">
+        <v>2024.0</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2">
+        <v>199.0</v>
+      </c>
+      <c r="B200" s="3">
+        <v>46268.0</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E200" s="4">
+        <v>2001.0</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4">
+        <v>200.0</v>
+      </c>
+      <c r="B201" s="3">
+        <v>46269.0</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E201" s="4">
+        <v>1975.0</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2">
+        <v>201.0</v>
+      </c>
+      <c r="B202" s="3">
+        <v>46270.0</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="E202" s="4">
+        <v>2005.0</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4">
+        <v>202.0</v>
+      </c>
+      <c r="B203" s="3">
+        <v>46270.0</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E203" s="4">
+        <v>1978.0</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2">
+        <v>203.0</v>
+      </c>
+      <c r="B204" s="3">
+        <v>46271.0</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E204" s="4">
+        <v>1977.0</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>2125</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
